--- a/maler/Mal.xlsx
+++ b/maler/Mal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9b03d2b7fbaaf455/Dokumenter/= Annet/Finsk studier/ordkaos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9b03d2b7fbaaf455/Dokumenter/Forpliktelser/Finsk studier/ordkaos/maler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_AD2441A7ACF4010922093233AB149DB825B98CB1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BD97D60-0AD2-4796-8B0D-71DA6794341E}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_AD2441A7ACF4010922093233AB149DB825B98CB1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECAFF462-00E2-472A-8F8D-BE3D7FF5ADD5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="9480" windowHeight="8240" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark 9" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
   <si>
     <t>1</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>Å Skje</t>
+  </si>
+  <si>
+    <t>Sist løst (E-N)</t>
+  </si>
+  <si>
+    <t>Sist løst (N-E)</t>
   </si>
 </sst>
 </file>
@@ -398,9 +404,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-tema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -438,7 +444,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -544,7 +550,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -686,7 +692,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -956,19 +962,20 @@
   <sheetPr>
     <tabColor rgb="FF5C8EDE"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="3" width="16.26953125" customWidth="1"/>
-    <col min="4" max="4" width="9.7265625" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" customWidth="1"/>
-    <col min="6" max="6" width="27.90625" customWidth="1"/>
-    <col min="7" max="7" width="26.36328125" customWidth="1"/>
-    <col min="8" max="8" width="12.7265625" customWidth="1"/>
-    <col min="9" max="9" width="5.36328125" customWidth="1"/>
+    <col min="4" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="7" max="7" width="10.1796875" customWidth="1"/>
+    <col min="8" max="8" width="27.90625" customWidth="1"/>
+    <col min="9" max="9" width="26.36328125" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" customWidth="1"/>
+    <col min="11" max="11" width="5.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -978,9 +985,11 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
         <v>45</v>
@@ -989,26 +998,32 @@
         <v>46</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -1017,10 +1032,12 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="9" t="s">
         <v>53</v>
@@ -1028,23 +1045,25 @@
       <c r="C4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10">
         <v>3.5</v>
       </c>
-      <c r="E4" s="10">
+      <c r="G4" s="10">
         <v>2.7</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7"/>
       <c r="B5" s="9" t="s">
         <v>57</v>
@@ -1052,21 +1071,23 @@
       <c r="C5" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10">
         <v>4.7</v>
       </c>
-      <c r="E5" s="10">
+      <c r="G5" s="10">
         <v>4.7</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K5" s="7"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7"/>
       <c r="B6" s="9" t="s">
         <v>59</v>
@@ -1074,21 +1095,23 @@
       <c r="C6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E6" s="10">
+      <c r="G6" s="10">
         <v>2.5</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K6" s="7"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
       <c r="B7" s="9" t="s">
         <v>61</v>
@@ -1096,21 +1119,23 @@
       <c r="C7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7">
         <v>4.2</v>
       </c>
-      <c r="E7" s="7">
+      <c r="G7" s="7">
         <v>4.0999999999999996</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K7" s="7"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="9" t="s">
         <v>64</v>
@@ -1118,21 +1143,23 @@
       <c r="C8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7">
         <v>5.6</v>
       </c>
-      <c r="E8" s="7">
+      <c r="G8" s="7">
         <v>6.1</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K8" s="7"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
       <c r="B9" s="5" t="s">
         <v>66</v>
@@ -1140,21 +1167,21 @@
       <c r="C9" t="s">
         <v>67</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>5.3</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>2.1</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="K9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="5" t="s">
         <v>69</v>
@@ -1162,43 +1189,45 @@
       <c r="C10" t="s">
         <v>70</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>7.2</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K10" s="7"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E11" s="5">
+      <c r="G11" s="5">
         <v>4.2</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="17" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
